--- a/outputs/hrp_weights/factor_momentum_weights.xlsx
+++ b/outputs/hrp_weights/factor_momentum_weights.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4035360715892181</v>
+        <v>0.447016637245269</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4035360715892181</v>
+        <v>0.447016637245269</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.04847175442475024</v>
+        <v>-0.05369453238467137</v>
       </c>
       <c r="C4" t="n">
         <v>-0.2402350512748825</v>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01118057708180197</v>
+        <v>-0.01238527190366339</v>
       </c>
       <c r="C5" t="n">
         <v>-0.05541302435626278</v>
@@ -543,16 +543,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1226573962608493</v>
+        <v>0.02812470049836727</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.6079129222713411</v>
+        <v>0.1258329026484794</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.002800557948826166</v>
+        <v>0.002583645534728785</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004606840628362462</v>
+        <v>0.02053235267048023</v>
       </c>
     </row>
     <row r="7">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.01061812905416223</v>
+        <v>-0.01176222072276006</v>
       </c>
       <c r="C7" t="n">
         <v>-0.05262542707691827</v>
@@ -675,19 +675,19 @@
         <v>42035</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.1485341859982744</v>
+        <v>-0.1408402533401543</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3968730820178711</v>
+        <v>0.376315425567648</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.205265153580656</v>
+        <v>-0.1946326095767686</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1565128257816787</v>
+        <v>-0.1484056070050511</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0928147526215197</v>
+        <v>0.139806104510378</v>
       </c>
       <c r="G5" t="inlineStr"/>
     </row>
@@ -696,19 +696,19 @@
         <v>42216</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.522488535238285</v>
+        <v>-0.4686949648680723</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01852141999040354</v>
+        <v>0.01661452014014051</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1926944733557047</v>
+        <v>-0.1728553323730537</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1330650271995832</v>
+        <v>-0.1193651229496066</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1332305442160236</v>
+        <v>0.2224700596691269</v>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
@@ -717,19 +717,19 @@
         <v>42400</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.4041263021731631</v>
+        <v>-0.465890648052456</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.06973171186412605</v>
+        <v>-0.0803891067111598</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1553648530480028</v>
+        <v>-0.1791099259856969</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1012138424070048</v>
+        <v>-0.1166827854987609</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2695632905077033</v>
+        <v>0.1579275337519263</v>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
@@ -738,19 +738,19 @@
         <v>42582</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.5555474716221777</v>
+        <v>-0.5063504035002222</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1052581436174165</v>
+        <v>-0.09593690227180129</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.181832817111913</v>
+        <v>-0.1657304281222899</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1378812375504753</v>
+        <v>-0.1256710251329781</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01948033009801763</v>
+        <v>-0.1063112409727085</v>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
@@ -759,19 +759,19 @@
         <v>42766</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3922743241787352</v>
+        <v>0.3007990247027868</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1368969322690213</v>
+        <v>-0.1049736400605271</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.243044882444771</v>
+        <v>-0.1863687197765203</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1743012214540169</v>
+        <v>-0.1336555420180491</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.05348263965345559</v>
+        <v>0.2742030734421168</v>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
@@ -780,19 +780,19 @@
         <v>42947</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1359041222351178</v>
+        <v>0.1103469722307651</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1522132060469519</v>
+        <v>-0.1235890872519727</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2588127540100042</v>
+        <v>-0.2101422923014918</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2154890433818306</v>
+        <v>-0.1749657265358842</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2375808743260956</v>
+        <v>0.3809559216798862</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
@@ -801,19 +801,19 @@
         <v>43131</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.2478722994826641</v>
+        <v>-0.2451853397242395</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.08287158980318428</v>
+        <v>-0.0819732537350453</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1920014920781509</v>
+        <v>-0.1899201772888493</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1975066699429811</v>
+        <v>-0.1953656784918797</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2797479486930197</v>
+        <v>0.2875555507599862</v>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
@@ -822,19 +822,19 @@
         <v>43312</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.3202720307412163</v>
+        <v>-0.387397232819022</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.08420738214723421</v>
+        <v>-0.1018562462394076</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2072609437683278</v>
+        <v>-0.2507003683758645</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.06798761260200541</v>
+        <v>-0.0822370062319621</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3202720307412163</v>
+        <v>0.1778091463337439</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
@@ -843,19 +843,19 @@
         <v>43496</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.3418765887917237</v>
+        <v>-0.2867401983137814</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.07932824975646725</v>
+        <v>-0.06653452974784468</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2097673981752015</v>
+        <v>-0.1759370115546775</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3486278874699206</v>
+        <v>0.2924026764866905</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02039987580668703</v>
+        <v>-0.1783855838970057</v>
       </c>
       <c r="G13" t="inlineStr"/>
     </row>
@@ -864,19 +864,19 @@
         <v>43677</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.2027407887924458</v>
+        <v>-0.2428532367112614</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1196919550866153</v>
+        <v>-0.1433731163532226</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2240476654503342</v>
+        <v>0.2683756981330384</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2607625967622541</v>
+        <v>0.3123547117189991</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1927569939083508</v>
+        <v>0.0330432370834786</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
@@ -908,22 +908,22 @@
         <v>44043</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.2161486945298504</v>
+        <v>-0.2491398998004169</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0481134853541902</v>
+        <v>-0.05545714234483316</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2161486945298504</v>
+        <v>0.2491398998004169</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2161486945298504</v>
+        <v>0.2491398998004169</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2161486945298504</v>
+        <v>0.09650791031592632</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08729173652640812</v>
+        <v>0.1006152479379898</v>
       </c>
     </row>
     <row r="17">
@@ -931,22 +931,22 @@
         <v>44227</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.2232416129910276</v>
+        <v>-0.2416540389998858</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0459043388475675</v>
+        <v>-0.04969041721885378</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2303271019019385</v>
+        <v>0.2493239218262535</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2303271019019385</v>
+        <v>0.2493239218262535</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2303271019019385</v>
+        <v>0.166846350722168</v>
       </c>
       <c r="G17" t="n">
-        <v>0.03987274245558965</v>
+        <v>0.04316134940658543</v>
       </c>
     </row>
     <row r="18">
@@ -954,22 +954,22 @@
         <v>44408</v>
       </c>
       <c r="B18" t="n">
-        <v>0.09035891407239921</v>
+        <v>0.0736813208753902</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.08424463505270637</v>
+        <v>-0.06869555761122913</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3291047495002578</v>
+        <v>0.2683617095056524</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2048372246740073</v>
+        <v>-0.1670303083361213</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1231989142422929</v>
+        <v>0.2850305605505515</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1682555624583365</v>
+        <v>-0.1372005431210555</v>
       </c>
     </row>
     <row r="19">
@@ -977,22 +977,22 @@
         <v>44592</v>
       </c>
       <c r="B19" t="n">
-        <v>0.06033624434943698</v>
+        <v>0.05559893269387187</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.2038689231109118</v>
+        <v>-0.1878621159906764</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1867339816446933</v>
+        <v>-0.1720725276998268</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.295943672628344</v>
+        <v>-0.2727075991065409</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1493050971916333</v>
+        <v>0.2160975686465044</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1038120810749806</v>
+        <v>-0.09566125586257959</v>
       </c>
     </row>
     <row r="20">
@@ -1000,22 +1000,22 @@
         <v>44773</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2113099853585854</v>
+        <v>0.1851533095149931</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1314389152776114</v>
+        <v>-0.1151689548480761</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1491772990435375</v>
+        <v>-0.130711620539595</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4246052928522873</v>
+        <v>0.3720461911715791</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.02667837643452222</v>
+        <v>-0.1471594703873629</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05679013103345632</v>
+        <v>0.04976045353839376</v>
       </c>
     </row>
     <row r="21">
@@ -1023,22 +1023,22 @@
         <v>44957</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2749012534456349</v>
+        <v>0.2992156131461323</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.07392791662498463</v>
+        <v>-0.08046666439058456</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.125005184989484</v>
+        <v>-0.1360615952246691</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3980982146260268</v>
+        <v>0.4333090514818773</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1207193893517741</v>
+        <v>0.04294911811071559</v>
       </c>
       <c r="G21" t="n">
-        <v>0.007348040962095488</v>
+        <v>0.007997957646021093</v>
       </c>
     </row>
     <row r="22">
@@ -1046,22 +1046,22 @@
         <v>45138</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.05387715667422335</v>
+        <v>-0.05557052028987226</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2257559302014309</v>
+        <v>0.232851458284541</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2257559302014309</v>
+        <v>0.232851458284541</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2257559302014309</v>
+        <v>0.232851458284541</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2257559302014309</v>
+        <v>0.2014213732507652</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.04309912252005311</v>
+        <v>-0.0444537316057395</v>
       </c>
     </row>
     <row r="23">
@@ -1069,22 +1069,22 @@
         <v>45322</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.03998717691762244</v>
+        <v>-0.0447613108507266</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2236844001133196</v>
+        <v>0.2503904435803797</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2236844001133196</v>
+        <v>0.2503904435803797</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2236844001133196</v>
+        <v>0.2503904435803797</v>
       </c>
       <c r="F23" t="n">
-        <v>0.190478173923056</v>
+        <v>0.09382804962385416</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.09848144881936285</v>
+        <v>-0.1102393087842802</v>
       </c>
     </row>
     <row r="24">
@@ -1092,22 +1092,22 @@
         <v>45504</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0320392384049514</v>
+        <v>0.03407451020919065</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2462061365154188</v>
+        <v>0.2618462213809526</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2462061365154188</v>
+        <v>0.2618462213809526</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2462061365154188</v>
+        <v>0.2618462213809526</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08529700506697614</v>
+        <v>0.02719109158331872</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1440453469818161</v>
+        <v>0.1531957340646327</v>
       </c>
     </row>
     <row r="25">
@@ -1115,22 +1115,22 @@
         <v>45688</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.03196087830633608</v>
+        <v>-0.03507085490511747</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3055644236630234</v>
+        <v>0.3352975930053607</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3055644236630234</v>
+        <v>0.3352975930053607</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.003662999986085594</v>
+        <v>-0.004019430874150532</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1036259200786059</v>
+        <v>0.01640358577382267</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2496213543029257</v>
+        <v>0.2739109424361879</v>
       </c>
     </row>
     <row r="26">
@@ -1138,22 +1138,22 @@
         <v>45869</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.01061812905416223</v>
+        <v>-0.01176222072276006</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4035360715892181</v>
+        <v>0.447016637245269</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4035360715892181</v>
+        <v>0.447016637245269</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.04847175442475024</v>
+        <v>-0.05369453238467137</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1226573962608493</v>
+        <v>0.02812470049836727</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.01118057708180197</v>
+        <v>-0.01238527190366339</v>
       </c>
     </row>
   </sheetData>
